--- a/src/attributions/attributions_ig_traj_332.xlsx
+++ b/src/attributions/attributions_ig_traj_332.xlsx
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05073173871442074</v>
+        <v>0.1620460529543912</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.009061868139488227</v>
+        <v>-0.00738798626620335</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0312696448115297</v>
+        <v>-0.0829480746132084</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03116121766116003</v>
+        <v>0.21794332651747</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,79 +2176,79 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01063874896148698</v>
+        <v>-0.04152405387803459</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.04827524781179004</v>
+        <v>-0.09467134924370818</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002171208602063457</v>
+        <v>-0.007115022443293081</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.001926237283427344</v>
+        <v>-0.02392833376219718</v>
       </c>
       <c r="X4" t="n">
-        <v>6.54445630713856e-12</v>
+        <v>-4.399214184792673e-11</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0135885406314294</v>
+        <v>-0.05036675538884921</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02647293872004262</v>
+        <v>-0.1251976252814005</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002206291865418289</v>
+        <v>-0.06438943328184166</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01246548764900511</v>
+        <v>0.1000645090819294</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,52 +2257,52 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.009900070526612237</v>
+        <v>-0.05510680268931454</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02058770554167406</v>
+        <v>-0.09237182935098333</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.07901018838205426</v>
+        <v>0.6956498828821901</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.004147202623194577</v>
+        <v>-0.1461273433221652</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07212894949844098</v>
+        <v>-0.1482714849096617</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02252771155582892</v>
+        <v>-0.04626526328312904</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,52 +2311,52 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02712414936525917</v>
+        <v>-0.07136821885509785</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.01982012595775389</v>
+        <v>-0.05850285353903948</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01845800309886982</v>
+        <v>0.09852065901291293</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.007197345366100576</v>
+        <v>0.1164017008912039</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01256712121898542</v>
+        <v>0.1085161484812276</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.03837777069060055</v>
+        <v>0.3079837014905311</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,148 +2365,148 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.0155409853808297</v>
+        <v>-0.1521505072659156</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01155018090673708</v>
+        <v>-0.2185741787857423</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02113388441307222</v>
+        <v>-0.1208677586452651</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001159694317166551</v>
+        <v>-0.008422248944566184</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03398702694357228</v>
+        <v>0.1028823346195341</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.004918058319427301</v>
+        <v>-0.1316584544140132</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.007569279297261219</v>
+        <v>0.09498078144463382</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.002475424065729619</v>
+        <v>0.04811454780660616</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0139748585906513</v>
+        <v>-0.1160715257295304</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003265748272880706</v>
+        <v>-0.020031222877568</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03575527638517534</v>
+        <v>0.09486852711390621</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01993565660341664</v>
+        <v>-0.04593687662539413</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01563972795319196</v>
+        <v>-0.1046110962285186</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05284671201092127</v>
+        <v>0.09286173956493919</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01070235084618218</v>
+        <v>-0.05009456560285563</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01181918432252689</v>
+        <v>0.0575482423645888</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.008343851599905416</v>
+        <v>0.12761390384083</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,115 +2518,115 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002712912444889249</v>
+        <v>0.01162362664763863</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002090705727004243</v>
+        <v>-0.01458021966009439</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02809196976289825</v>
+        <v>-0.05015986783016242</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.00621544896135188</v>
+        <v>-0.1010069593125674</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>5.253678662441097e-05</v>
+        <v>-0.09175920432571784</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01547518581863192</v>
+        <v>0.02865014538117579</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.007945415379118614</v>
+        <v>-0.01954106343335127</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.002059974757128421</v>
+        <v>-0.08895406599662792</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03703504620981968</v>
+        <v>0.09929422229079225</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01665228462209176</v>
+        <v>-0.14313915886235</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.0002265650515275106</v>
+        <v>-0.0401686903425053</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03351457600290878</v>
+        <v>0.08852212868080764</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01589381819342347</v>
+        <v>-0.1527662004418306</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,52 +2635,52 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.009383888805572029</v>
+        <v>0.02538061283479076</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.006181035385843601</v>
+        <v>0.02132523601747932</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001494771551091919</v>
+        <v>0.07131821580976587</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007259156052607849</v>
+        <v>-0.01354638758120814</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03344864563700672</v>
+        <v>0.1119253171830791</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02053560032634036</v>
+        <v>0.003582235464576021</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.007124303183818631</v>
+        <v>0.08273131820503089</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.120732707086409</v>
+        <v>0.1772105953773903</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01751615176287274</v>
+        <v>-0.05524334770915189</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03815993789536147</v>
+        <v>-0.05252409480266385</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06352386714783066</v>
+        <v>0.1584842876347478</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0050486469338349</v>
+        <v>-0.02088965044155001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0505366653557975</v>
+        <v>-0.07771473737562211</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,109 +2760,109 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01874785179820941</v>
+        <v>0.02626890418974156</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.007435072692708723</v>
+        <v>-0.0006820596714422299</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0105734834384836</v>
+        <v>-0.003166457650233133</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03216571708484338</v>
+        <v>-0.02522881174106215</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01662699618707869</v>
+        <v>-0.06760225233652269</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.03488258559280059</v>
+        <v>-0.08189432168692129</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002311423037906336</v>
+        <v>0.1001455377799544</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03846261219226659</v>
+        <v>-0.01233723991815941</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.06505413448277575</v>
+        <v>0.07344265756048898</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3309074165875001</v>
+        <v>0.3147239747296073</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0266549337979013</v>
+        <v>-0.1456780809349316</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1195665406500668</v>
+        <v>-0.1436529716205737</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.01057305348434581</v>
+        <v>-0.003030680411643403</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03656755909911736</v>
+        <v>-0.009697229182958445</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.07665749662110231</v>
+        <v>-0.03298444499112686</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,28 +2889,28 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.09812450174497737</v>
+        <v>-0.01898403092147279</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.04041624796514907</v>
+        <v>0.03572389787709475</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1229437607784086</v>
+        <v>0.07054321256382337</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2925,52 +2925,52 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1660622415954537</v>
+        <v>0.2418761692368311</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0105056275819278</v>
+        <v>-0.1362765117218348</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.02393521587133362</v>
+        <v>-0.0207937744944242</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05345070854968942</v>
+        <v>-0.1172953489686332</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01452243289265946</v>
+        <v>0.08356039420048536</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01011502481202406</v>
+        <v>0.02760100229407504</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,22 +2979,22 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01233330782207847</v>
+        <v>-0.04010738622816264</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.004646063176539195</v>
+        <v>0.0111384335984478</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.03581704542274585</v>
+        <v>0.01642549354310585</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
@@ -3003,25 +3003,25 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03490031497408784</v>
+        <v>-0.1252260184870482</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02299205390356017</v>
+        <v>0.09502095711276154</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02129276288252495</v>
+        <v>0.03111874715619058</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001694445936959804</v>
+        <v>-0.006671574607689086</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.009196208898524924</v>
+        <v>0.05438266205155041</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.04324870923045434</v>
+        <v>-0.06913628884798471</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,73 +3060,73 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07039063268546886</v>
+        <v>-0.07202924251109115</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002327690947933099</v>
+        <v>0.0745244090046184</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.006384053633839489</v>
+        <v>-0.03052325213709157</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01634142620028842</v>
+        <v>0.06531621537383402</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02954057605224916</v>
+        <v>0.0515830963317537</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02515061323581668</v>
+        <v>-0.06174896402291332</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04472602367675903</v>
+        <v>-0.0492436824936614</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0128299541465501</v>
+        <v>0.07164116960054451</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0578841630572443</v>
+        <v>0.02068584645479113</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03777218214625174</v>
+        <v>-0.08049054025801332</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02999814895863513</v>
+        <v>0.08002513998574691</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.003166278058382827</v>
+        <v>-0.06435030646957712</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03549063391344655</v>
+        <v>-0.1330817197463436</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02372738818915765</v>
+        <v>0.1073264449653379</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02299993997412304</v>
+        <v>0.01623565629678916</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,19 +3192,19 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.02372774061444633</v>
+        <v>-0.05067811916155276</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.04325071857824567</v>
+        <v>0.01191067270389519</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.003783272673161545</v>
+        <v>0.04764465418641416</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,31 +3213,31 @@
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.05778701431796687</v>
+        <v>-0.00197968752600368</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.01605774659612588</v>
+        <v>0.1672407456839038</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.033248889974295</v>
+        <v>-0.08559251831675288</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01850775872719179</v>
+        <v>-0.07549160816098263</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.004226824336054941</v>
+        <v>0.02301276647573408</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02075325243371043</v>
+        <v>0.04160906575921641</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.004462857198888648</v>
+        <v>0.01664275205988452</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.00184847391316394</v>
+        <v>-0.005213460262797068</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01047973103551619</v>
+        <v>0.06967399243454381</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.009280877969980884</v>
+        <v>0.008855735343773305</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.007300979938622733</v>
+        <v>-0.01349610764193181</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>6.237340830785819e-05</v>
+        <v>-0.008691223390422534</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001250922278959429</v>
+        <v>-0.01117307077760983</v>
       </c>
       <c r="X6" t="n">
-        <v>6.371818933789328e-12</v>
+        <v>3.127870896680524e-13</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0161991028333597</v>
+        <v>-0.01724479284725529</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01660054066545273</v>
+        <v>-0.05611724917458205</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002789304302605437</v>
+        <v>-0.02668567811122099</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005314175906192686</v>
+        <v>0.004129282986575616</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01305486385079545</v>
+        <v>-0.02390895708538294</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.007051400745345513</v>
+        <v>-0.04507222167864722</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.04821149879011304</v>
+        <v>0.1532525657499661</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.00129857213279719</v>
+        <v>-0.042846324900897</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01152339539348196</v>
+        <v>-0.0346734055791203</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.004705573751630554</v>
+        <v>-0.01057671667831096</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01553646331462979</v>
+        <v>-0.01074198523260712</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.002215336546293565</v>
+        <v>-0.008266514586908637</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.01797925896699246</v>
+        <v>0.03255462821790337</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -3476,25 +3476,25 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.009395689952312467</v>
+        <v>0.06342664814110924</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01028846487540136</v>
+        <v>0.04427252785865354</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01286620016848678</v>
+        <v>0.04043281537108066</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.00883714269249134</v>
+        <v>-0.01233983123940417</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01549978359452945</v>
+        <v>-0.05342011273661385</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.003820178568186128</v>
+        <v>-0.019113504722804</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0004794067320136263</v>
+        <v>0.003239982040733166</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.00635223263149118</v>
+        <v>0.03216118278571155</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,73 +3548,73 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.002826136549778989</v>
+        <v>-0.02011936376263241</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003742752563579067</v>
+        <v>0.03600120521896105</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.007506715894736009</v>
+        <v>0.02313095209792743</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0002316988119415102</v>
+        <v>-0.02229439393766192</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-2.894698107745939e-06</v>
+        <v>-0.003339418583080658</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.00880926801409624</v>
+        <v>0.02746901247048619</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.005917123852575183</v>
+        <v>-0.002465297474889261</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001304584697382355</v>
+        <v>-0.00137003093475477</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01126996788730654</v>
+        <v>0.001793951194526654</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.005743005008391147</v>
+        <v>-0.01098794743290957</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01116869888005113</v>
+        <v>-0.007261516789509609</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002845717696592021</v>
+        <v>0.04129189377690401</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,46 +3656,46 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.005756821124709335</v>
+        <v>-6.987412279462289e-05</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.00643064594030704</v>
+        <v>-0.01126271973184389</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.005365557992427055</v>
+        <v>0.01404800693258513</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001564250651438007</v>
+        <v>-0.01621919977352627</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001582721337618032</v>
+        <v>-0.0108573080605097</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.008198264863497352</v>
+        <v>-0.001334621755805031</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,22 +3707,22 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.003235895434232502</v>
+        <v>-0.004434970108745476</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.008881044523213925</v>
+        <v>-0.01468191536285503</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02936960272974701</v>
+        <v>0.0363664943850374</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,52 +3731,52 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.001996510201184926</v>
+        <v>-0.02701586952070421</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.001946269456356395</v>
+        <v>-0.008928248317851309</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009543402743552833</v>
+        <v>0.0221100654159563</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.007355970808354348</v>
+        <v>-0.02126318938494882</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01464861573104116</v>
+        <v>0.02109990273979901</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01669977645085803</v>
+        <v>-0.00582784886795909</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.001245381030882384</v>
+        <v>0.02967653688210386</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0009123254650240487</v>
+        <v>-0.002295130103374437</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001361191832015536</v>
+        <v>-0.03644417399118047</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3815,22 +3815,22 @@
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01570381689170857</v>
+        <v>0.007809568009735215</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.0009161386886722363</v>
+        <v>0.0144362134067244</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.09096484747838936</v>
+        <v>0.05690555655632315</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008370720227754303</v>
+        <v>-0.02154751281944038</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.75310186517396e-11</v>
+        <v>-9.594494648711034e-12</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04022374041269448</v>
+        <v>0.08523259571774164</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05568063883202949</v>
+        <v>-0.02710737991154162</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,49 +3895,49 @@
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01493916144773037</v>
+        <v>-0.002240024545842567</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01248528891567353</v>
+        <v>-0.00496772697173102</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.006809428212689798</v>
+        <v>-0.01639596327147094</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.10479619565803e-12</v>
+        <v>-5.150734893011635e-13</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04031979640087657</v>
+        <v>-0.02745114443935575</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.04334076809365513</v>
+        <v>-0.03101669424164473</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01501815667202584</v>
+        <v>-0.0001818966516811522</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02711052516175548</v>
+        <v>0.02981603519202702</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02769623715674093</v>
+        <v>-0.01066721961397468</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01925861408430231</v>
+        <v>-0.01403533193455301</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2026997789941081</v>
+        <v>0.1255092034296432</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09437733139762081</v>
+        <v>-0.02883644593524991</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004682364253547737</v>
+        <v>0.0141774952710537</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01163578271813984</v>
+        <v>-0.007558093447014944</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06356120920459496</v>
+        <v>-0.02329580711246328</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.004935690430617552</v>
+        <v>-0.003316549138613165</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03078173371707039</v>
+        <v>0.0190762954369296</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.09630323672964902</v>
+        <v>0.04234776025951176</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.03485303562920299</v>
+        <v>0.01564594274324072</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1026039799725474</v>
+        <v>0.07158182553401618</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.009183778993956015</v>
+        <v>-0.02658907837923481</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.003764119659134923</v>
+        <v>-0.01897657840684837</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02557721366386845</v>
+        <v>-0.02760874959129041</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003463649696341436</v>
+        <v>0.007922704138387448</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03057327059506915</v>
+        <v>0.01379430589243186</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01184024319813866</v>
+        <v>-0.02080890682521945</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.004656453108360922</v>
+        <v>0.005079883496117498</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.003705487882906883</v>
+        <v>0.01440889721513901</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01879044444232701</v>
+        <v>-0.029050130074539</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,25 +4153,25 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.007844262613480675</v>
+        <v>0.004215180067796739</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03076291359934567</v>
+        <v>0.01285551066946329</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09050920660622627</v>
+        <v>-0.01781515081605176</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
@@ -4180,106 +4180,106 @@
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03053462441461266</v>
+        <v>-0.00780985511336223</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01621211984387072</v>
+        <v>-0.010126712641997</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0002884562231248386</v>
+        <v>-0.02100685128334558</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0007644181411154572</v>
+        <v>0.01063343808685813</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.007391587594763137</v>
+        <v>-0.03262541387042009</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.008823860926377419</v>
+        <v>0.0107830138002897</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01851094211836615</v>
+        <v>-0.008668557223237689</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01101961505308869</v>
+        <v>0.005054420385641792</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.003758687523829439</v>
+        <v>-0.01928537701481057</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02739611836138908</v>
+        <v>-0.005041680673734427</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03185656607962808</v>
+        <v>0.005558190077856402</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0372259849718174</v>
+        <v>-0.004981428335050261</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001711156544643216</v>
+        <v>-0.006948879531271053</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.007273497457428265</v>
+        <v>0.009817176812266086</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02917188462713969</v>
+        <v>-0.03290144683659007</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01014867156076045</v>
+        <v>-0.001217357927694481</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,70 +4327,70 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01761262464037206</v>
+        <v>0.01324916457285101</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03878417513242315</v>
+        <v>-0.02167125230828461</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02525921247410412</v>
+        <v>0.003160462991356588</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01409274836495257</v>
+        <v>0.05901047383193509</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.06818940756258277</v>
+        <v>0.01189936245568789</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01281429333808115</v>
+        <v>-0.0195895494729567</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0.0003373185861960757</v>
+        <v>0.001445552677484235</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03090778858014484</v>
+        <v>-0.008413365744366824</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03937850447986568</v>
+        <v>0.005615609214252647</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2347711877638805</v>
+        <v>0.1646036571730644</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09168037802406806</v>
+        <v>-0.1040805220148887</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.00513514788009012</v>
+        <v>-0.02264465546281641</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1603569296116676</v>
+        <v>0.176688275411153</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1045656559203108</v>
+        <v>-0.1557277931129253</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06687903998471845</v>
+        <v>-0.06523630216870471</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,100 +5036,100 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05732059070426937</v>
+        <v>0.05131041937388111</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002836548349299357</v>
+        <v>-0.0165858081437805</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01595365293934321</v>
+        <v>-0.03585464282961184</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.114734495189674</v>
+        <v>0.03992889638269937</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04796842299181603</v>
+        <v>-0.1211351908743177</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03032594948889759</v>
+        <v>-0.05651100234318812</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01743970870817466</v>
+        <v>0.1411404517212025</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0414079789253427</v>
+        <v>-0.1216683418291146</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.08004478105204987</v>
+        <v>0.1396762603882226</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4092636996106548</v>
+        <v>0.2752980567362959</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03090020720012882</v>
+        <v>-0.1565761626540043</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1849725994155881</v>
+        <v>-0.2878095316262443</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01394345044998565</v>
+        <v>-0.0724567651644963</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.07686597406154171</v>
+        <v>0.01863600489294876</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1437434254762206</v>
+        <v>-0.01996799017310743</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1162529179921532</v>
+        <v>0.015439653757438</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01983233144442862</v>
+        <v>0.01096062862873018</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1340954036198648</v>
+        <v>-0.04271907419834078</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,43 +5201,43 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2113240750494355</v>
+        <v>0.2420264357077585</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.008086557734068989</v>
+        <v>-0.2286736257831153</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.05410663366390473</v>
+        <v>-0.06083445470203863</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.0765620763165695</v>
+        <v>-0.0912298211283962</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001228352712270427</v>
+        <v>0.1399018591039576</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01602051048971085</v>
+        <v>0.01300314385068008</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,16 +5255,16 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.03185158609625387</v>
+        <v>-0.04134010462197013</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.05435306913997542</v>
+        <v>0.1731266555369375</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.02554177534159993</v>
+        <v>0.07323684184533852</v>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
@@ -5273,55 +5273,55 @@
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05039405463098726</v>
+        <v>-0.07539018644523145</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02032295625275827</v>
+        <v>0.1548227537694609</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001596248089598107</v>
+        <v>0.02865614442287161</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01377169180684963</v>
+        <v>-0.003448334505011605</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01985773745373938</v>
+        <v>0.01286114834742445</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.0005016436248589094</v>
+        <v>-0.06134759748094864</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5333,106 +5333,106 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05647043859739722</v>
+        <v>-0.1004061049210511</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.02129307263081406</v>
+        <v>0.1360216337497669</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01055942146746483</v>
+        <v>0.03060802420126078</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.02189763229919646</v>
+        <v>0.04371706812758209</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02457460405560874</v>
+        <v>0.04455411366422498</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02804150017780774</v>
+        <v>-0.02154199748924412</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01707722243110385</v>
+        <v>0.01065026992665073</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0311315287139422</v>
+        <v>0.09593484138198578</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04498372791329724</v>
+        <v>0.05181865062953196</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07551664496516727</v>
+        <v>-0.04698695268595388</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.04884407721368363</v>
+        <v>-0.1013352064620912</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.001892459371550675</v>
+        <v>0.000502635688900767</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,25 +5444,25 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.06088456881336879</v>
+        <v>-0.09009710625480996</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.00998625337406331</v>
+        <v>0.178561407764457</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01277227706873317</v>
+        <v>0.01108653698950172</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
@@ -5471,67 +5471,67 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03004583986912764</v>
+        <v>-0.05351520018348858</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03156300974619614</v>
+        <v>0.04014147610726647</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.02670507463947194</v>
+        <v>-0.08146113083794936</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03049443899187557</v>
+        <v>0.03151838462026114</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.03591822250184214</v>
+        <v>0.1772927071712944</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.03534355658249257</v>
+        <v>-0.152142503130492</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02907744695211392</v>
+        <v>-0.01076537205207906</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.06386801765803315</v>
+        <v>0.07417281729261516</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,27 +5543,27 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4159088701967574</v>
+        <v>0.2025603107869105</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.130936785889397</v>
+        <v>-0.2659398318261018</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08933763617060168</v>
+        <v>-0.0668012170995248</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.002875864575891533</v>
+        <v>-0.01185070620975307</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2869124641058518</v>
+        <v>0.1250694336259381</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1167328628399965</v>
+        <v>-0.3796158788151342</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1657942370053986</v>
+        <v>-0.1585460550642111</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,88 +5599,88 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0001951290808922268</v>
+        <v>-0.001685600701781443</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.147306198695478</v>
+        <v>0.1181662001544981</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.06167643553584475</v>
+        <v>-0.07325550293342653</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03694212438312522</v>
+        <v>-0.153760294625315</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.755241919773159e-11</v>
+        <v>1.478053877480875e-11</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06443980862538663</v>
+        <v>-0.0432724624814402</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03915501542050086</v>
+        <v>-0.09567565974948131</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04261894656307411</v>
+        <v>-0.1934788102865835</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01190461132507686</v>
+        <v>0.02825170853432931</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.05910453351442963</v>
+        <v>0.2529588792041398</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06825540648333864</v>
+        <v>-0.080598799109855</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.08916274485923786</v>
+        <v>0.142987457866157</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01854112105993828</v>
+        <v>0.02905918349366946</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,43 +5689,43 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6533956820396917</v>
+        <v>0.3404687974803198</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.0282525903606475</v>
+        <v>-0.2276274549759538</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1676826975527894</v>
+        <v>-0.6336428060969749</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.08715984164838163</v>
+        <v>-0.03199422329336115</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01489622646936439</v>
+        <v>-0.1016163546507147</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.04588249823093551</v>
+        <v>-0.04503240650462555</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3467319083543766</v>
+        <v>-0.01678787484632221</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-1.18024310787182e-11</v>
+        <v>4.18916987640311e-11</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1520990047291977</v>
+        <v>-0.03210527106027443</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1456512413175183</v>
+        <v>0.1370936305402035</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.07907082294136153</v>
+        <v>-0.119823502159624</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0309160319663942</v>
+        <v>-0.02109042844258256</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,133 +5770,133 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3385730081155459</v>
+        <v>0.2584951617073879</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.01511484634423603</v>
+        <v>-0.3460570669575853</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01046051598879153</v>
+        <v>-0.3017725459900165</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01335669589781508</v>
+        <v>-0.0443624823346081</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1119083495091153</v>
+        <v>-0.07747225343548299</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.04802225689833774</v>
+        <v>0.2715178388063607</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01620214799194559</v>
+        <v>0.05405058848629078</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.004846337273660263</v>
+        <v>-0.0690297898763258</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.01564718720373452</v>
+        <v>0.01241077548880665</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04820336901062271</v>
+        <v>0.1373581823232562</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.009873626860831833</v>
+        <v>0.2703408508571722</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.03954443132768562</v>
+        <v>0.02245448444088498</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.07543020147416163</v>
+        <v>-0.07418569215199734</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.08123621387219854</v>
+        <v>0.2955396150963572</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02472427405147938</v>
+        <v>0.07885481074488739</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.00469286005838159</v>
+        <v>-0.04431508022116851</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.09223468668669454</v>
+        <v>-0.08405430374422133</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.05768319998890661</v>
+        <v>0.09817183806018567</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.001755148538675349</v>
+        <v>0.0021062838368633</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01303338239717335</v>
+        <v>-0.07944231786238318</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,16 +5905,16 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1036585408170459</v>
+        <v>-0.0264375326872448</v>
       </c>
       <c r="DP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.01347661424921769</v>
+        <v>0.1568908377221581</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01849148762823195</v>
+        <v>-0.08921844070093256</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,7 +5923,7 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.004270260548689606</v>
+        <v>0.1388333234944451</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,16 +5932,16 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.0301023317697216</v>
+        <v>0.07193818649807862</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.02547900604712122</v>
+        <v>0.1624417785503347</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.04957432994821064</v>
+        <v>-0.1072177033572341</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,25 +5950,25 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.001806307950683692</v>
+        <v>0.2352895709512991</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.05663592895669849</v>
+        <v>0.05526580949428571</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07346351078682456</v>
+        <v>0.1643376875928537</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02590548285285708</v>
+        <v>0.04488034332142879</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,106 +5977,106 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.04690184228045533</v>
+        <v>-0.05390722040644986</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.0732413921741871</v>
+        <v>-0.09191734366713812</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.106872598318224</v>
+        <v>0.2512676452050306</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.06871009382087795</v>
+        <v>0.01432009136566504</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.04411205927005585</v>
+        <v>0.007611638831587139</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0861863009028575</v>
+        <v>-0.08541275886628304</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.06897601415351656</v>
+        <v>0.3352385544926735</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.008134753513358316</v>
+        <v>0.08210464637626774</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.000819169301612803</v>
+        <v>-0.06015529157239288</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01421274508875647</v>
+        <v>-0.04246794248634419</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.08514611446590573</v>
+        <v>-0.1141582385352696</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03311648974774567</v>
+        <v>0.04809452306135947</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01959213824716515</v>
+        <v>-0.0835394275955116</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.07253155482535213</v>
+        <v>0.1684631025167029</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.05047597951341685</v>
+        <v>0.2939144713947474</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1007835409687247</v>
+        <v>-0.2074020837583099</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,25 +6085,25 @@
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.03522578873962781</v>
+        <v>-0.2136277589965478</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1089907047541396</v>
+        <v>0.02848564276997904</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.00515078774779295</v>
+        <v>0.172055823018783</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>-0</v>
@@ -6112,7 +6112,7 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.009321453960728782</v>
+        <v>-0.06365396234965436</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.215719451539212</v>
+        <v>0.5334739314521061</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03278519360418562</v>
+        <v>0.05859243031370716</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.232947526409763</v>
+        <v>-0.3791850667483383</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,25 +6150,25 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1749197168361824</v>
+        <v>0.7601497767991261</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03564739388621432</v>
+        <v>-0.1022922200823283</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2263328425970082</v>
+        <v>-0.3942711869928793</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0240452058050665</v>
+        <v>0.1876939029718272</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.007341801420324156</v>
+        <v>-0.187612695118201</v>
       </c>
       <c r="X11" t="n">
-        <v>0.008572631710052224</v>
+        <v>-0.02109122550109107</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0422099807136507</v>
+        <v>0.04474673315287692</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02344614649936618</v>
+        <v>-0.4918691594158141</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0005871933268656822</v>
+        <v>-0.1023041784341528</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04140056231188484</v>
+        <v>0.2070142087552667</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0002221925413109535</v>
+        <v>-0.02518266304833901</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.05060481890749483</v>
+        <v>-0.1111002050392811</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2344809617997174</v>
+        <v>1.015762632441687</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.007988885487074502</v>
+        <v>-0.3678493573740262</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.1203603589505952</v>
+        <v>-0.1805030887608201</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,67 +6279,67 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.08416469944123046</v>
+        <v>-0.09145712343665967</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.09950226614711849</v>
+        <v>-0.1329935869097251</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.127634887069511</v>
+        <v>-0.232120487023165</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1013933800643372</v>
+        <v>0.1993325473915855</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0368065699349007</v>
+        <v>0.1420585340749095</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.008636641225519888</v>
+        <v>0.01695613348640364</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1039417561263516</v>
+        <v>0.6477846885063524</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,13 +6348,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01142888221524175</v>
+        <v>-0.1159787918041208</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.05180318268420474</v>
+        <v>-0.2218970967075705</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6366,46 +6366,46 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.05417016026242841</v>
+        <v>-0.264445586537251</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.0001768646171900557</v>
+        <v>0.001986452037216522</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0606851416814185</v>
+        <v>0.1702480437884077</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.00567800677169022</v>
+        <v>-0.2409013572040239</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01519807464828248</v>
+        <v>0.1838948711383487</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01591487166534684</v>
+        <v>0.1111269120960381</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.03490108273947382</v>
+        <v>-0.2293240483645184</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.002695550533745042</v>
+        <v>-0.04614283487609502</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.05832052141445337</v>
+        <v>0.1681479298458634</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6444,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04219388321566082</v>
+        <v>-0.08019820356812778</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02829170966780375</v>
+        <v>-0.2932829886882026</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003117320372367507</v>
+        <v>-0.02088002170844499</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,67 +6468,67 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0186152478444328</v>
+        <v>-0.1549407512086749</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02221908688990039</v>
+        <v>-0.05680576897923319</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.01983171794295544</v>
+        <v>0.03106511131970807</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.006019259935494855</v>
+        <v>0.0983635953633625</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01890781485116119</v>
+        <v>-0.009039967412647456</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01164373744926778</v>
+        <v>0.09752935243944522</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02191515112300602</v>
+        <v>0.007624658346470432</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,37 +6537,37 @@
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.00936567676063493</v>
+        <v>-0.1314476419994779</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.04713427375430514</v>
+        <v>0.1147935263762953</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.02713364856390415</v>
+        <v>-0.05552647303315879</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.001046095228236011</v>
+        <v>-0.194935129039192</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.05280447401175334</v>
+        <v>0.154603865039469</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
@@ -6576,106 +6576,106 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03634651677316217</v>
+        <v>-0.290578451764294</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.00326072387468134</v>
+        <v>-0.04069696270023648</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.06260054605396748</v>
+        <v>0.1492150252402848</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.0208335763096019</v>
+        <v>-0.2814098018019734</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01979240559254179</v>
+        <v>0.2197210264153279</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03485938299615548</v>
+        <v>0.1508444202114843</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.006699839518582927</v>
+        <v>0.1838067688359009</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.04875238633306139</v>
+        <v>-0.1084959232196223</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03451532493188116</v>
+        <v>0.135815798627392</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.03101028323582827</v>
+        <v>-0.04494106304636593</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03072281362173907</v>
+        <v>0.07222193346206356</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2538020249575009</v>
+        <v>0.4770144922080951</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1310118014825873</v>
+        <v>-0.2364567601017447</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05460536824213515</v>
+        <v>-0.06087423345900148</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6716,19 +6716,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1902871545163914</v>
+        <v>0.5005846376001081</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1189598091002437</v>
+        <v>-0.3102587296861196</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09305197899117729</v>
+        <v>-0.1832200550138617</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,115 +6737,115 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09028807206287298</v>
+        <v>0.1246097225307872</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.006430445929234046</v>
+        <v>-0.06543967069809223</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03462126403420714</v>
+        <v>-0.1103330691933804</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1059555792225788</v>
+        <v>-0.1130452926050243</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02429406830710975</v>
+        <v>-0.1582798595177647</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02325203526529827</v>
+        <v>-0.1387346623008499</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04102829716457777</v>
+        <v>0.2231671231361877</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.03875593386246366</v>
+        <v>-0.1242714060873804</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06725463044527488</v>
+        <v>0.1376984481389385</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3647202332740173</v>
+        <v>0.4391861685964459</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.02078550619339207</v>
+        <v>-0.137859303622167</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08107145840133687</v>
+        <v>-0.360142691587367</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.00107738264806418</v>
+        <v>-0.02120180198442476</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.07290849153466036</v>
+        <v>-0.0782503818357901</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1720891615951031</v>
+        <v>-0.04214979229600888</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,52 +6881,52 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.08675453903482537</v>
+        <v>-0.0326061209515866</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05477532599636076</v>
+        <v>0.05081934682110426</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09280986611157091</v>
+        <v>0.04793691084942597</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1811884235456059</v>
+        <v>0.3747570920110934</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.01885819113629943</v>
+        <v>-0.1844030536584599</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05373996568153188</v>
+        <v>-0.110758024301045</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07023298395207932</v>
+        <v>-0.1952406651011014</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01503230077652326</v>
+        <v>0.1856479949814677</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.005684050419114266</v>
+        <v>0.01816241958602146</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.02228974152325285</v>
+        <v>-0.04479056379294767</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03268246110229597</v>
+        <v>0.1983043238587963</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.02512228850232372</v>
+        <v>0.0673804013941587</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04404694947351464</v>
+        <v>-0.1785112073931419</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03195664402089225</v>
+        <v>0.200358219025496</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.001494903828507413</v>
+        <v>0.04313969632072532</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7016,79 +7016,79 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03198479829102457</v>
+        <v>-0.1271756588018128</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.02169875901243108</v>
+        <v>0.03045140948601932</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01353463530648585</v>
+        <v>-0.1128119801054199</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04648212179717425</v>
+        <v>-0.1154249905307113</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.002322056063299487</v>
+        <v>0.1261403384742691</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.02806889831251985</v>
+        <v>-0.004482973495163278</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02209207729431895</v>
+        <v>0.04037095976770266</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.014033044639058</v>
+        <v>-0.05718591823823554</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.008221239279644925</v>
+        <v>0.02475611043846438</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,49 +7097,49 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02459715416604476</v>
+        <v>-0.1015339407647006</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.05572064737383472</v>
+        <v>0.147574297249485</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0458402832747958</v>
+        <v>0.0515092354128957</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06004204689822055</v>
+        <v>-0.1251489244595845</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02740078091640382</v>
+        <v>0.1511810809947285</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04644567201076226</v>
+        <v>-0.04572391060547396</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,22 +7151,22 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.05292406538509472</v>
+        <v>-0.2067021060544277</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.03586868783208244</v>
+        <v>0.2193829919449823</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003125605284041271</v>
+        <v>0.008809753303429518</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,19 +7178,19 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01649332419271867</v>
+        <v>-0.1301260582340698</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.04405445411284184</v>
+        <v>0.08186548358357022</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.0396127430347176</v>
+        <v>0.003186517639379067</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
@@ -7199,22 +7199,22 @@
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01784110664690405</v>
+        <v>0.007410652462921779</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001715777651729214</v>
+        <v>0.205941604696484</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01800732564672529</v>
+        <v>0.04685319414937902</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7226,42 +7226,42 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.008222356322095786</v>
+        <v>-0.1507618207852495</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03724862097811327</v>
+        <v>0.1442755539269771</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.3851089804901887</v>
+        <v>-0.1848882338058582</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -7270,10 +7270,10 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1293531061434318</v>
+        <v>0.00886681379384517</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7563917508325028</v>
+        <v>0.2889552385815434</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7285,22 +7285,22 @@
         <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.280500440656009</v>
+        <v>-0.2161068185559429</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0001054960593275816</v>
+        <v>0.07873765284413702</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6875168256593649</v>
+        <v>0.2802133323097595</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7312,49 +7312,49 @@
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0250362658015933</v>
+        <v>-0.1204714117363951</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2057429795918668</v>
+        <v>0.1554281812368672</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1105989167046282</v>
+        <v>0.04691031557232603</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.03107713249268931</v>
+        <v>-0.003989252104899747</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.04368089188243945</v>
+        <v>0.2749083565772046</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.07868279802912678</v>
+        <v>0.1671682767979196</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,22 +7369,22 @@
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.05242257909122145</v>
+        <v>-0.1147468069475643</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04947480699513093</v>
+        <v>-0.06062369425123819</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1394112506320013</v>
+        <v>0.1266944218737486</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.3957172105935142</v>
+        <v>-0.5053039311645</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -7405,25 +7405,25 @@
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2441371776905863</v>
+        <v>0.057342399071483</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.6437097496073316</v>
+        <v>0.1762759524795618</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.215997140996857</v>
+        <v>0.1252846053566791</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,40 +7432,40 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.04049127736631849</v>
+        <v>0.2039284077990386</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2272600390375337</v>
+        <v>0.137181001046897</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.2050995660849115</v>
+        <v>-0.02696997724516571</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.1096346002437886</v>
+        <v>-0.1027037699263085</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03091505980378849</v>
+        <v>-0.01488941238431093</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,25 +7477,25 @@
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2367081709720373</v>
+        <v>-0.3228720362005186</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1737001860276948</v>
+        <v>0.07961655596352171</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.35235425695687</v>
+        <v>0.2133913845283681</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,49 +7504,49 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.09253064527906193</v>
+        <v>0.1049106855414718</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01512702379293618</v>
+        <v>-0.03631469685955981</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.1629477407782392</v>
+        <v>-0.1121460677754619</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01873725335902082</v>
+        <v>0.1186741583076654</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.09731071522043709</v>
+        <v>-0.1614340834920301</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.004461439392047593</v>
+        <v>-0.09684668479131539</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.06483400306102759</v>
+        <v>0.09764507282207138</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02875878388097874</v>
+        <v>-0.02654163840877043</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.1556894007097566</v>
+        <v>-0.1037006618128092</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,49 +7585,49 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.03941487075752195</v>
+        <v>0.03599938679389834</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
         <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.1949444450580975</v>
+        <v>0.0986660944198758</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.03149395687885471</v>
+        <v>-0.008191882486428357</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.006515963872604148</v>
+        <v>0.06063329537155284</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.02935835950776869</v>
+        <v>0.01301544865990522</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.002458739052799416</v>
+        <v>-0.07180628345417979</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
@@ -7636,49 +7636,49 @@
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.02254386698593879</v>
+        <v>-0.05394559640616746</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01936113964426218</v>
+        <v>0.06629251347508675</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.1065697140928529</v>
+        <v>-0.0450114939069964</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.06209405378470684</v>
+        <v>0.02358604034266755</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.08855701177938601</v>
+        <v>0.02658150139799748</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1403991799821892</v>
+        <v>-0.04976231834029912</v>
       </c>
       <c r="EL13" t="n">
         <v>0</v>
@@ -7687,55 +7687,55 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0242446928611809</v>
+        <v>0.008211104555760995</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.005873515475465813</v>
+        <v>0.03371749853954068</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.1557158549122865</v>
+        <v>-0.07395962771941099</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.05706330133827851</v>
+        <v>0.1184951918777651</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.07168312330156784</v>
+        <v>-0.0277104354077707</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.1542250999838171</v>
+        <v>-0.1055563978518438</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.06176186833650924</v>
+        <v>0.1429316059315064</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0243564643480885</v>
+        <v>-0.06299220173050725</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02643157790158806</v>
+        <v>0.05794738275509911</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01109861297884082</v>
+        <v>-0.04104969391960446</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,28 +7783,28 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.008441116633379151</v>
+        <v>0.02749905605374851</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0501914297554087</v>
+        <v>0.05757110399831655</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.02964564389363531</v>
+        <v>0.05920249511729105</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
         <v>0</v>
@@ -7813,13 +7813,13 @@
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02838556378548363</v>
+        <v>-0.005778845243369008</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1718189728779962</v>
+        <v>0.165131866179179</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -7836,25 +7836,25 @@
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1119981729098626</v>
+        <v>-0.2630426643800343</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1085928568610091</v>
+        <v>0.124215638824343</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1622655178038572</v>
+        <v>0.1056922933311577</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7863,25 +7863,25 @@
         <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.03858679198062701</v>
+        <v>-0.3361916480643498</v>
       </c>
       <c r="N14" t="n">
-        <v>0.05102244742999536</v>
+        <v>0.06074331870645954</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03645129677684913</v>
+        <v>-0.02372545639946313</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -7890,40 +7890,40 @@
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05975966303264901</v>
+        <v>-0.05512894282906269</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04164408929765993</v>
+        <v>-0.07012011006014729</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.02148401684059368</v>
+        <v>0.0565056573895411</v>
       </c>
       <c r="AC14" t="n">
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01337116980043242</v>
+        <v>0.07100179731987202</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02397573194503859</v>
+        <v>0.2332234341545651</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7932,49 +7932,49 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.01167717167676426</v>
+        <v>0.04517947778049938</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.02216538449117626</v>
+        <v>-0.1533458409459394</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06139862228301438</v>
+        <v>0.07125614809390311</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1136665514123651</v>
+        <v>-0.1023291514039761</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.07444079825058575</v>
+        <v>-0.3760586655542856</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1597481966540818</v>
+        <v>-0.008203302811208126</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7989,7 +7989,7 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.1109082855224972</v>
+        <v>0.188949994081572</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -7998,37 +7998,37 @@
         <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0001911530304130537</v>
+        <v>0.2504600970586498</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.06999080378094881</v>
+        <v>0.2059071245916863</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.05241434047031007</v>
+        <v>-0.01739660878457672</v>
       </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.01313696484277989</v>
+        <v>0.01322693348336467</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.10505679081605</v>
+        <v>-0.1232799325530614</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,25 +8037,25 @@
         <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.06467075305022432</v>
+        <v>-0.08107243498536233</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.01560712461637712</v>
+        <v>-0.2970574724540473</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.08122569375042819</v>
+        <v>-0.06154305227850503</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,13 +8064,13 @@
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.03167472754986586</v>
+        <v>-0.06674542862311038</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
@@ -8079,10 +8079,10 @@
         <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.01264060167983138</v>
+        <v>0.1090263869699566</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02567930385950694</v>
+        <v>-0.04379992479912813</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8097,34 +8097,34 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.02239430663506179</v>
+        <v>0.01203443229110535</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.06568911298480125</v>
+        <v>0.1004129321226968</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.07043356334040066</v>
+        <v>-0.06032828621765473</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.02175154064005948</v>
+        <v>-0.06028098601052261</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
@@ -8133,10 +8133,10 @@
         <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0009885559782112708</v>
+        <v>0.1114161337236192</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01470668757315542</v>
+        <v>-0.0226175027889742</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8148,10 +8148,10 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.01798624950906793</v>
+        <v>-0.01730209128940065</v>
       </c>
       <c r="DF14" t="n">
         <v>-0</v>
@@ -8160,10 +8160,10 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0750946527953705</v>
+        <v>0.1246365250691016</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.02641118039748334</v>
+        <v>-0.01650456029762297</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8178,79 +8178,79 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.0234958137637556</v>
+        <v>-0.08289735087765376</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.03681225530222768</v>
+        <v>0.0355191145291336</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.06655966960781814</v>
+        <v>-0.003435220388828746</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.03996376736383249</v>
+        <v>0.006279944858536026</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02365154207226329</v>
+        <v>-0.004443775455435723</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02216878564396906</v>
+        <v>0.006613443319215155</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.02373117537508749</v>
+        <v>-0.09587528624961088</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01487067321483362</v>
+        <v>0.09571653557290222</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.009434749953873977</v>
+        <v>0.01698120052546524</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,22 +8259,22 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0.009614901561347231</v>
+        <v>0.03574875710475686</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0199044463827133</v>
+        <v>0.1425640730327049</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.006426188200675419</v>
+        <v>0.005897189506592082</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8286,19 +8286,19 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.02267507688106702</v>
+        <v>-0.06622805735192894</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.008291494852606208</v>
+        <v>0.1535068004318583</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.02507287181457483</v>
+        <v>-0.03133767395452739</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
@@ -8310,10 +8310,10 @@
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.01577414788270292</v>
+        <v>0.02905031501430139</v>
       </c>
       <c r="FH14" t="n">
         <v>0</v>
@@ -8322,10 +8322,10 @@
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.02393219954718961</v>
+        <v>0.130542591699813</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.1173181824528978</v>
+        <v>0.1429596391412251</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
@@ -8334,55 +8334,55 @@
         <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.006845432113405612</v>
+        <v>-0.002414879457281568</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.004880586868035616</v>
+        <v>0.2508740050730966</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0499783088954413</v>
+        <v>0.06251240196299118</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.02229574876643774</v>
+        <v>0.02238019072223139</v>
       </c>
       <c r="FZ14" t="n">
         <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.019358411645213</v>
+        <v>0.2192448718999084</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -9537,25 +9537,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.464006037743842</v>
+        <v>0.314145788800321</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.213690755922597</v>
+        <v>-0.2630150233388923</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05623636678274033</v>
+        <v>-0.04154194224357333</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -9564,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3091686772893197</v>
+        <v>0.3346466621589709</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2493368450749698</v>
+        <v>-0.3735854753679781</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0678724014983766</v>
+        <v>-0.1534833559616527</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9591,76 +9591,76 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09973576278518753</v>
+        <v>0.04239057501050498</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.00436861355272419</v>
+        <v>-0.07294956953102974</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1397611844091128</v>
+        <v>-0.1039332299772386</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.08363278850976616</v>
+        <v>-0.06682054282775272</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.03235867436458721</v>
+        <v>-0.1338630572404317</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.04178331435940076</v>
+        <v>-0.1111889495151816</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.01050531881593712</v>
+        <v>0.1179148448985517</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.06186637562024456</v>
+        <v>-0.1377015329322635</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01192210134947837</v>
+        <v>0.0439053542363767</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9672,25 +9672,25 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.3966580425402422</v>
+        <v>0.2855782200138257</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.06127107439789742</v>
+        <v>-0.08313622975428614</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1306370379137497</v>
+        <v>-0.2868230995938325</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,25 +9699,25 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05347188316916103</v>
+        <v>-0.003958388697119392</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.2043371808784797</v>
+        <v>-0.03629547620714586</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1681918769594767</v>
+        <v>0.0001280487735494992</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,100 +9726,100 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1016645978499683</v>
+        <v>0.01919082380468094</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>-0.0001228360759275198</v>
+        <v>0.0864378286743905</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1742894553249103</v>
+        <v>0.0411381760555535</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1625996662776479</v>
+        <v>0.1935117731056679</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.03388422312014398</v>
+        <v>-0.177872122119126</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.111371108770046</v>
+        <v>-0.08123479082683041</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.09082279854626153</v>
+        <v>-0.09253252183449084</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.005380913520061375</v>
+        <v>0.1395649095756381</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01251183687505771</v>
+        <v>0.02445692973514838</v>
       </c>
       <c r="CI17" t="n">
         <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.004471039862110992</v>
+        <v>-0.05299729123237797</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.1611631133197839</v>
+        <v>0.2214959968904062</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.07520678045576151</v>
+        <v>0.08158954412880533</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.06708394399390694</v>
+        <v>-0.09133530370410042</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03345121933472785</v>
+        <v>0.1498347754292303</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.0207512881300389</v>
+        <v>0.03738589086240092</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
@@ -9852,25 +9852,25 @@
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.02276686092105686</v>
+        <v>-0.05329882527686556</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.05207944114056191</v>
+        <v>0.04766981810766879</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02337216052914406</v>
+        <v>-0.108959657820695</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.03742764311262105</v>
+        <v>-0.07721900347951557</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.006384190694356076</v>
+        <v>-0.05025921361606409</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.02685428571379275</v>
+        <v>0.01445738803957813</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,43 +9915,43 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.04277621502120528</v>
+        <v>0.003240517300027538</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.03336448705702407</v>
+        <v>0.08065633073837666</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.0598049975572133</v>
+        <v>-0.03292810342281537</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0821178888512053</v>
+        <v>-0.04641045118374427</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0.006177931725444511</v>
+        <v>0.09254687899837809</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.07160918356618702</v>
+        <v>0.06485023233454647</v>
       </c>
       <c r="EK17" t="n">
         <v>0</v>
@@ -9963,22 +9963,22 @@
         <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01779063133182174</v>
+        <v>-0.007266316837973302</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.02072505532524003</v>
+        <v>0.1090937149759125</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01708695067292624</v>
+        <v>-0.04375244540309369</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
@@ -9993,28 +9993,28 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.06403190689084767</v>
+        <v>-0.09736494345671873</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0.004942794769620109</v>
+        <v>0.1746218877951349</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.0005639592097789705</v>
+        <v>0.01246709101308247</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.004321361019999555</v>
+        <v>0.125077116228017</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.01939565078559337</v>
+        <v>0.10757702137438</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.003135083571775055</v>
+        <v>-0.01407417221039569</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10041,58 +10041,58 @@
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.02165836749609637</v>
+        <v>0.03496786334179784</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.05039422313082665</v>
+        <v>0.1584954460029219</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.03165644400317966</v>
+        <v>-0.02622348279367825</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
         <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.05240979100968161</v>
+        <v>0.005008782147926162</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.1042547420564951</v>
+        <v>0.07283237799855399</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2236901653674261</v>
+        <v>0.3001322921636938</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,25 +10115,25 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05706061209626856</v>
+        <v>-0.09135508956989125</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1617953627012015</v>
+        <v>-0.1319340739498126</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1894659379273365</v>
+        <v>0.3535880951010277</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,16 +10142,16 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03440012274583153</v>
+        <v>-0.1661039552421609</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1572062772066234</v>
+        <v>-0.1704022747110988</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01877541559012363</v>
+        <v>0.0849127845967244</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,37 +10169,37 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.01920831889176585</v>
+        <v>-0.08580655888182631</v>
       </c>
       <c r="X18" t="n">
-        <v>0.009138828299600209</v>
+        <v>-0.01314652604439954</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.00848575968395603</v>
+        <v>-0.03109536897300313</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.02742348770272005</v>
+        <v>-0.1913024772993715</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002690648894797191</v>
+        <v>0.05869339158131007</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02408351570625542</v>
+        <v>0.0261588855561148</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
@@ -10223,13 +10223,13 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.005351731095185492</v>
+        <v>-0.05513934396092914</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.02687203259610787</v>
+        <v>0.007218524906040805</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1507701256935356</v>
+        <v>0.325403788038968</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,13 +10250,13 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.02255599841015753</v>
+        <v>-0.2849790876054651</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.05540035372147048</v>
+        <v>-0.1081432161501736</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
         <v>-0</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.05177891918719758</v>
+        <v>-0.02083280208588419</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,52 +10277,52 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.0591959157212214</v>
+        <v>-0.002289110482997798</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.07844582386224749</v>
+        <v>-0.0158573346596869</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05058529276217728</v>
+        <v>0.04296811656162763</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.01499947708081137</v>
+        <v>0.07367428613705772</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01835980282120872</v>
+        <v>0.001271637541390187</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.07648627615069933</v>
+        <v>0.1835113648794773</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.02136754829659425</v>
+        <v>-0.09442367329778883</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.03302888841011239</v>
+        <v>-0.08767966675369208</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,28 +10343,28 @@
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.03589458903815913</v>
+        <v>-0.07971635082407591</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.002269519853894627</v>
+        <v>0.05636328192540326</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.03804311726017649</v>
+        <v>0.03991224878989466</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,46 +10376,46 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.0008833799638143314</v>
+        <v>-0.07430892715676077</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0005760952829363495</v>
+        <v>0.1648058136748959</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.0282599015719155</v>
+        <v>0.04995210890273311</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.02875121916033409</v>
+        <v>-0.0822749848321611</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.0007255696105070718</v>
+        <v>0.0491636997255585</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.03768351293579356</v>
+        <v>0.06189966806030817</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10430,61 +10430,61 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.01453064425495513</v>
+        <v>-0.01687385474716499</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.02416277996837621</v>
+        <v>-0.07884678407686009</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.005194844261149644</v>
+        <v>0.04428853090956416</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.006998714500046086</v>
+        <v>-0.007331338967655068</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01749878985250384</v>
+        <v>-0.04896019345731065</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.007969609502787918</v>
+        <v>0.01156828736014513</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.03712041572962683</v>
+        <v>0.007334845666263781</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
@@ -10493,124 +10493,124 @@
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01241889268291696</v>
+        <v>-0.002517558847856746</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.01743653030606074</v>
+        <v>0.004172812544999852</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.0396685130155616</v>
+        <v>-0.04088749416789738</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.008875487575524388</v>
+        <v>0.04928649703502855</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.03571096574975172</v>
+        <v>0.002591240419361371</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.01226075680706109</v>
+        <v>-0.01101919938868806</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.009776754541435605</v>
+        <v>0.0005804424173340167</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.02035008030565537</v>
+        <v>0.06598920450031359</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.02847507285626069</v>
+        <v>-0.09515425465040804</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.001882318909216545</v>
+        <v>0.03893302414733084</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03905761169621512</v>
+        <v>0.03423806547610069</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01241297234233389</v>
+        <v>0.1516319441997835</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.001274956631300459</v>
+        <v>-0.08911261657924267</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.02248705960427439</v>
+        <v>0.08228287976847067</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,46 +10619,46 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.009821790994192531</v>
+        <v>0.06475810057214321</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.02405241553919783</v>
+        <v>-0.1204972415412001</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.02105405408501342</v>
+        <v>-0.01791404398405924</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.0116913527863489</v>
+        <v>-0.04511954878923748</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02008225222196747</v>
+        <v>0.07989598954662305</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,22 +10675,22 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4782714593545428</v>
+        <v>0.2787697413280091</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1894115948988301</v>
+        <v>-0.2562016884638672</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.09490629691274956</v>
+        <v>-0.0390825857985256</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
         <v>-0</v>
@@ -10702,16 +10702,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3054795686575793</v>
+        <v>0.2961233514432616</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2197097344254202</v>
+        <v>-0.3339087059594285</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.09949893958016359</v>
+        <v>-0.1206789739700246</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10723,82 +10723,82 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1077960096535445</v>
+        <v>0.04939615563797634</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.006828486107908502</v>
+        <v>-0.05870504833904768</v>
       </c>
       <c r="W19" t="n">
-        <v>0.09388041128651994</v>
+        <v>-0.07736894678672469</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.05856527514848074</v>
+        <v>-0.06924667145094</v>
       </c>
       <c r="AD19" t="n">
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.01073816182508737</v>
+        <v>-0.1205968490127256</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.01830959913707527</v>
+        <v>-0.08829266054450023</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.01287809739128203</v>
+        <v>0.0966971677690404</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.0589707505191921</v>
+        <v>-0.107514901345928</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.05266308354040482</v>
+        <v>0.02487839446953209</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10810,25 +10810,25 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.3955811274091116</v>
+        <v>0.2427157928301581</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.03227531954540133</v>
+        <v>-0.09519385881972617</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.08510792053750782</v>
+        <v>-0.2390413670597198</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
@@ -10837,25 +10837,25 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.02417466746100158</v>
+        <v>-0.007896421841567794</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.1882588326087855</v>
+        <v>-0.05762712830362857</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.1222923605297916</v>
+        <v>0.009771889395360835</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,19 +10864,19 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1533617734419133</v>
+        <v>0.03014638008469126</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.04130492429331169</v>
+        <v>0.07552079533560024</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1641448300559005</v>
+        <v>0.03995745653928606</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
         <v>0</v>
@@ -10885,85 +10885,85 @@
         <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.1844227469771434</v>
+        <v>0.1544431758830736</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.01822151604457413</v>
+        <v>-0.1484496519527016</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.05605173382089629</v>
+        <v>-0.06450638767352505</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.07923880815693203</v>
+        <v>-0.06227530183812247</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.004831706402358455</v>
+        <v>0.1233851424323814</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.004544984842683445</v>
+        <v>0.02050600238500529</v>
       </c>
       <c r="CI19" t="n">
         <v>-0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.01574379932668527</v>
+        <v>-0.05167269093715902</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.08951030982185573</v>
+        <v>0.1957251092383614</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.08893722397694123</v>
+        <v>0.06693215239769025</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
         <v>-0</v>
@@ -10972,43 +10972,43 @@
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.05251758135050987</v>
+        <v>-0.06100184200581311</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.03457433797983273</v>
+        <v>0.1291003131840144</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.01279026147411001</v>
+        <v>0.02886042133822795</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.04505374610212851</v>
+        <v>-0.07876833667303913</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.03943452991075673</v>
+        <v>0.0295246829344965</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.03326546437488605</v>
+        <v>-0.03229007108705032</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
@@ -11023,28 +11023,28 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.04342295432720455</v>
+        <v>-0.05343621754597525</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.01135203416512043</v>
+        <v>-0.02422208438085761</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.03556450625359007</v>
+        <v>-0.001139233054871698</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
         <v>0</v>
@@ -11053,16 +11053,16 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.09779877077169984</v>
+        <v>0.03853368331197899</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>-0.01483689547975089</v>
+        <v>0.08663854317643559</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.04032926498103225</v>
+        <v>-0.0829599092134749</v>
       </c>
       <c r="EB19" t="n">
         <v>-0</v>
@@ -11074,55 +11074,55 @@
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
         <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.06771867336228811</v>
+        <v>-0.02836909565790375</v>
       </c>
       <c r="EH19" t="n">
         <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.015212052951692</v>
+        <v>0.08588784125485617</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.05665713826190658</v>
+        <v>0.05177194517823833</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.0002038601761399163</v>
+        <v>-0.008255728819407518</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.0002849429368399326</v>
+        <v>0.09346798494054351</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.03778278063671914</v>
+        <v>-0.02382320754177679</v>
       </c>
       <c r="ET19" t="n">
         <v>0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11131,25 +11131,25 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.05089368823424342</v>
+        <v>-0.06978839110742938</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.001197502785281838</v>
+        <v>0.1526749685896442</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01542012996633939</v>
+        <v>0.008645321512134001</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
@@ -11161,16 +11161,16 @@
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.06070096715971212</v>
+        <v>0.1299822643010408</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.004776559500658016</v>
+        <v>0.09274991753879444</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.04627201818263581</v>
+        <v>-0.06604358025352582</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11179,31 +11179,31 @@
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.04319925203532338</v>
+        <v>0.04807682952170628</v>
       </c>
       <c r="FR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.02396726819214683</v>
+        <v>0.1695312302705575</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.0518789332825917</v>
+        <v>-0.05191771399308842</v>
       </c>
       <c r="FU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
         <v>0</v>
@@ -11212,25 +11212,25 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.05615709330700719</v>
+        <v>0.01759791951194175</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.1078446001861136</v>
+        <v>0.04180810623934257</v>
       </c>
       <c r="GC19" t="n">
         <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
         <v>0</v>
